--- a/tests/fixtures/data.xlsx
+++ b/tests/fixtures/data.xlsx
@@ -483,7 +483,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C3:C4">
+    <dataValidation type="list" sqref="C3:C4">
       <formula1>"Active,Inactive,Pending"</formula1>
     </dataValidation>
   </dataValidations>
